--- a/docs/Decodifiche/147_dmnm_dec_ruolo_vittima.xlsx
+++ b/docs/Decodifiche/147_dmnm_dec_ruolo_vittima.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
   <si>
     <t>ID</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Pedone</t>
   </si>
   <si>
-    <t>2025-12-02 20:23:11.0</t>
+    <t>2025-12-04 11:48:12.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>Passeggero</t>
-  </si>
-  <si>
-    <t>2025-12-02 20:23:12.0</t>
   </si>
   <si>
     <t>4</t>
@@ -202,7 +199,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
@@ -213,53 +210,53 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
